--- a/test/fixtures/hospital-sample.xlsx
+++ b/test/fixtures/hospital-sample.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>Actualizado: 30JUN26 00:40h</t>
         </is>
       </c>
     </row>
@@ -538,9 +538,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Alta médica</t>
@@ -566,9 +563,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>FALLECIDO | ⚠ ESTADO EN CONFLICTO</t>
